--- a/5_Audit_and_Metrics/MT-ISMS-AUD-001_v1.0_internal-audit-checklist.xlsx
+++ b/5_Audit_and_Metrics/MT-ISMS-AUD-001_v1.0_internal-audit-checklist.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="87">
   <si>
     <t>MunichTech GmbH</t>
   </si>
@@ -49,7 +49,7 @@
     <t>Effective Date</t>
   </si>
   <si>
-    <t>[Date]</t>
+    <t/>
   </si>
   <si>
     <t>Classification</t>
@@ -233,7 +233,7 @@
     <t>Risk RR-013 (Key Person Dependency) is scored as a 12 (High) and marked as Accepted. However the CEO signature column in the Risk Register was left blank. Auditee must obtain formal CEO sign-off within 7 days.</t>
   </si>
   <si>
-    <t>Tabletop exercise conducted on [Date]. Evidence provided showing the IT Security Lead successfully drafted a mock 24-hour early warning report using the BSI portal template.</t>
+    <t>Tabletop exercise conducted on 19 March 2026. Evidence provided showing the IT Security Lead successfully drafted a mock 24-hour early warning report using the BSI portal template.</t>
   </si>
   <si>
     <t>Auditor observed AWS Security Hub actively running the CIS AWS Foundations Benchmark. Overall compliance score is 94 percent. High-severity deviations are configured to trigger Slack alerts to the DevOps team.</t>
@@ -275,13 +275,13 @@
     <t>Signature: ___________________________</t>
   </si>
   <si>
-    <t>Date of Audit Completion: [Date]</t>
+    <t>Date of Audit Completion: 14 April 2026</t>
   </si>
   <si>
     <t>Acknowledged by CISO / Head of Engineering:</t>
   </si>
   <si>
-    <t>Date: [Date]</t>
+    <t>Date: 15 April 2026</t>
   </si>
   <si>
     <t>CAP Owner</t>
@@ -293,19 +293,28 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>[Date of Audit + 7 Days]</t>
+    <t/>
   </si>
   <si>
     <t>Head of Engineering</t>
   </si>
   <si>
-    <t>[Date of Audit + 90 Days]</t>
+    <t/>
   </si>
   <si>
     <t>CISO / Head of Engineering</t>
   </si>
   <si>
     <t>Intune successfully enforces Apple FileVault encryption and a 5-minute screen lock. HR Manager provided the formal document ⁠MT-WorksCouncil-CrowdStrike-v1.2.pdf signed by the Betriebsrat explicitly permitting CrowdStrike deployment for security purposes only.</t>
+  </si>
+  <si>
+    <t>14 April 2026</t>
+  </si>
+  <si>
+    <t>21 April 2026</t>
+  </si>
+  <si>
+    <t>13 July 2026</t>
   </si>
 </sst>
 </file>
@@ -917,7 +926,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.2">
@@ -1060,7 +1069,7 @@
         <v>82</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="2:10" s="5" customFormat="1" ht="119" x14ac:dyDescent="0.2">
@@ -1164,7 +1173,7 @@
         <v>80</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="2:10" s="5" customFormat="1" ht="187" x14ac:dyDescent="0.2">
